--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M04/run_1/CF_M04_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M04/run_1/CF_M04_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.6757</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.5208</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.6552</v>
       </c>
       <c r="D3" t="n">
+        <v>0.5278</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9826</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.75</v>
       </c>
       <c r="D4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.86</v>
       </c>
     </row>
@@ -1201,7 +1215,6 @@
       <c r="D2" t="n">
         <v>0.7577</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1222,7 +1235,6 @@
           <t>['AU_11', 'AU_15', 'AU_22']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_49</t>
@@ -1233,7 +1245,6 @@
           <t>presentation, backend, authentication</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1252,7 +1263,6 @@
           <t>CF_M04_AU01, CF_M04_AU21</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M04_AU21</t>
@@ -1283,7 +1293,6 @@
       <c r="D3" t="n">
         <v>0.7596000000000001</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1304,7 +1313,6 @@
           <t>['AU_15', 'AU_18']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_45</t>
@@ -1315,7 +1323,6 @@
           <t>backend, mysql</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1334,7 +1341,6 @@
           <t>CF_M04_AU04, CF_M04_AU10</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M04_AU25</t>
@@ -1385,14 +1391,11 @@
           <t>71</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Presentation Layer</t>
@@ -1416,13 +1419,11 @@
           <t>CF_M04_AU01</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M04_AU02</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1443,7 +1444,6 @@
       <c r="D5" t="n">
         <v>0.869</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1464,7 +1464,6 @@
           <t>['AU_15', 'AU_20', 'AU_21', 'AU_23']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_54</t>
@@ -1475,7 +1474,6 @@
           <t>backend, gemini, chatgpt, notifications</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1494,7 +1492,6 @@
           <t>CF_M04_AU09, CF_M04_AU013, CF_M04_AU14</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M04_AU16</t>
@@ -1545,14 +1542,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Authentication Service</t>
@@ -1571,14 +1565,11 @@
       <c r="P6" t="n">
         <v>68</v>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M04_AU18</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1599,7 +1590,6 @@
       <c r="D7" t="n">
         <v>0.9006999999999999</v>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1620,7 +1610,6 @@
           <t>['AU_11', 'AU_15', 'AU_22']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_48</t>
@@ -1631,7 +1620,6 @@
           <t>presentation, backend, authentication</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1650,7 +1638,6 @@
           <t>CF_M04_AU04, CF_M04_AU18</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M04_AU19</t>
@@ -1681,7 +1668,6 @@
       <c r="D8" t="n">
         <v>0.9288</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1702,7 +1688,6 @@
           <t>['AU_15', 'AU_19', 'AU_22']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_46</t>
@@ -1713,7 +1698,6 @@
           <t>backend, artificial intelligence, authentication</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1732,7 +1716,6 @@
           <t>CF_M04_AU01, CF_M04_AU013, CF_M04_AU14</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M04_AU15</t>
@@ -1763,7 +1746,6 @@
       <c r="D9" t="n">
         <v>0.9443</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1784,7 +1766,6 @@
           <t>['AU_11', 'AU_15']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_44</t>
@@ -1795,7 +1776,6 @@
           <t>presentation, backend</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1814,7 +1794,6 @@
           <t>CF_M04_AU01, CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M04_AU29</t>
@@ -1865,14 +1844,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_15</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Backend</t>
@@ -1891,14 +1867,11 @@
       <c r="P10" t="n">
         <v>55</v>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1939,14 +1912,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -1965,14 +1935,11 @@
       <c r="P11" t="n">
         <v>54</v>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M04_AU01</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2013,14 +1980,11 @@
           <t>65</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>AU_08</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Domain Layer</t>
@@ -2044,13 +2008,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M04_AU07</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2096,13 +2058,11 @@
           <t>['AU_45']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_18</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -2126,13 +2086,11 @@
           <t>CF_M04_AU10</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M04_AU11</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2173,14 +2131,11 @@
           <t>71</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Domain</t>
@@ -2204,13 +2159,11 @@
           <t>CF_M04_P08</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M04_AU22</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2256,13 +2209,11 @@
           <t>['AU_23', 'AU_54']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Firebase</t>
@@ -2281,14 +2232,11 @@
       <c r="P15" t="n">
         <v>56</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M04_AU27</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2329,14 +2277,11 @@
           <t>65</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Infrastructure Layer</t>
@@ -2360,13 +2305,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M04_AU09</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2412,13 +2355,11 @@
           <t>['AU_47', 'AU_53']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>AU_30</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2442,13 +2383,11 @@
           <t>CF_M04_AU06</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M04_AU17</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2489,14 +2428,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Factory Pattern</t>
@@ -2520,13 +2456,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M04_P06</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2567,14 +2501,11 @@
           <t>65</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Application Layer</t>
@@ -2598,13 +2529,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M04_AU08</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2645,14 +2574,11 @@
           <t>71</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_13</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Data</t>
@@ -2676,13 +2602,11 @@
           <t>CF_M04_P08</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M04_AU23</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2728,13 +2652,11 @@
           <t>['AU_45']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_17</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Django</t>
@@ -2758,13 +2680,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M04_AU05</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2810,13 +2730,11 @@
           <t>['AU_19', 'AU_46', 'AU_50', 'AU_54']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_20</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Gemini</t>
@@ -2835,14 +2753,11 @@
       <c r="P22" t="n">
         <v>55</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M04_AU14</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2883,14 +2798,11 @@
           <t>66</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>P_03</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Repository Pattern</t>
@@ -2914,13 +2826,11 @@
           <t>CF_M04_AU09</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M04_P05</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2966,13 +2876,11 @@
           <t>['AU_19', 'AU_46', 'AU_54']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>AU_21</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>ChatGPT</t>
@@ -2991,14 +2899,11 @@
       <c r="P24" t="n">
         <v>55</v>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M04_AU13</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3039,14 +2944,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>P_01</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>Hexagonal Architecture</t>
@@ -3072,13 +2974,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3119,14 +3019,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Flutter</t>
@@ -3150,13 +3047,11 @@
           <t>CF_M04_AU01, CF_M04_AU03</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M04_AU03</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3230,7 +3125,6 @@
           <t>Localboss</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Localboss, una start-up que desenvolupa una aplicació mòbil destinada a ajudar els propietaris de negocis a gestionar les seves ressenyes a Google Maps.</t>
@@ -3266,7 +3160,6 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Localboss, una start-up que desenvolupa una aplicació mòbil destinada a ajudar els propietaris de negocis a gestionar les seves ressenyes a Google Maps.</t>
@@ -3302,7 +3195,6 @@
           <t>Google Maps</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Localboss, una start-up que desenvolupa una aplicació mòbil destinada a ajudar els propietaris de negocis a gestionar les seves ressenyes a Google Maps.</t>
@@ -3338,7 +3230,6 @@
           <t>Cintia</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>incorporació de l’agent d’intel·ligència artificial Cintia en lloc de la funcionalitat Share Review</t>
@@ -3374,7 +3265,6 @@
           <t>Capa de Domini</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Capa de Domini (Domain Layer): conté la lògica de negoci més pura del sistema, així com els models de domini i les interfícies dels repositoris.</t>
@@ -3410,7 +3300,6 @@
           <t>Capa d’Aplicació</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Capa d’Aplicació (Application Layer): inclou els casos d’ús del sistema, que orquestren la lògica de negoci i defineixen el flux de les operacions.</t>
@@ -3446,7 +3335,6 @@
           <t>Capa d’Infraestructura</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Capa d’Infraestructura (Infrastructure Layer): és la responsable de la interacció amb l’exterior.</t>
@@ -3482,7 +3370,6 @@
           <t>Artificial Intelligence</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>serveis d’intel·ligència artificial (Gemini ou ChatGPT)</t>
@@ -3518,7 +3405,6 @@
           <t>Notifications</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Firebase per a funcionalitats complementàries (notificacions, serveis associats)</t>
@@ -3554,7 +3440,6 @@
           <t>Jira</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Jira per a la gestió de requisits i tasques</t>
@@ -3590,7 +3475,6 @@
           <t>Git</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>Git com a sistema de control de versions</t>
@@ -3626,7 +3510,6 @@
           <t>Android Studio</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>Android Studio i VS Code com a entorns de desenvolupament</t>
@@ -3662,7 +3545,6 @@
           <t>VS Code</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>Android Studio i VS Code com a entorns de desenvolupament</t>
@@ -3698,7 +3580,6 @@
           <t>Google OAuth 2.0</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>destacant el mètode principal mitjançant Google OAuth 2.0</t>
@@ -3734,7 +3615,6 @@
           <t>GET</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>utilitzant mètodes HTTP estàndard com GET i POST</t>
@@ -3770,7 +3650,6 @@
           <t>POST</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>utilitzant mètodes HTTP estàndard com GET i POST</t>
@@ -3806,7 +3685,6 @@
           <t>syncfusion_flutter_charts</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>syncfusion_flutter_charts: utilitzada per a la creació de gràfics avançats a la nova pantalla Home</t>
@@ -3842,7 +3720,6 @@
           <t>fl_chart</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
           <t>fl_chart: emprada per a la implementació de gràfics lineals</t>
@@ -3878,7 +3755,6 @@
           <t>SliverAppBar</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>SliverAppBar: utilitzada per implementar una App Bar avançada</t>
@@ -3914,7 +3790,6 @@
           <t>video_player</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>video_player: incorporada per permetre la reproducció de vídeos associats a les reviews</t>
@@ -3950,7 +3825,6 @@
           <t>Postman</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>Postman per provar i validar els endpoints del backend</t>
@@ -3986,7 +3860,6 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
           <t>GitHub per a la gestió del codi, pull requests i revisions</t>
@@ -4017,7 +3890,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>backend, frontend</t>
@@ -4053,7 +3925,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>presentation, google oauth 2.0</t>
@@ -4089,7 +3960,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>presentation, backend</t>
@@ -4105,7 +3975,6 @@
           <t>CF_M04_AU21</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>0.6825</v>
       </c>
@@ -4121,7 +3990,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>presentation, backend</t>
@@ -4137,7 +4005,6 @@
           <t>CF_M04_AU19</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
         <v>0.7573</v>
       </c>
@@ -4153,7 +4020,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>presentation, backend</t>
@@ -4169,7 +4035,6 @@
           <t>CF_M04_AU28</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
         <v>0.7356</v>
       </c>
@@ -4185,7 +4050,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>presentation, backend</t>
@@ -4201,7 +4065,6 @@
           <t>CF_M04_AU29</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
         <v>0.8701</v>
       </c>
@@ -4217,7 +4080,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>presentation, backend, gemini</t>
@@ -4233,7 +4095,6 @@
           <t>CF_M04_AU15</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
         <v>0.7336</v>
       </c>
@@ -4249,7 +4110,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>data, backend</t>
@@ -4265,7 +4125,6 @@
           <t>CF_M04_AU29</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
         <v>0.673</v>
       </c>
@@ -4281,7 +4140,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
           <t>data, backend</t>
@@ -4297,7 +4155,6 @@
           <t>CF_M04_AU19</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
         <v>0.731</v>
       </c>
@@ -4313,7 +4170,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
           <t>presentation, backend</t>
@@ -4329,7 +4185,6 @@
           <t>CF_M04_AU29</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
         <v>0.9265</v>
       </c>
@@ -4350,7 +4205,6 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
           <t>La comunicació entre el front-end i el back-end es realitza mitjançant una API REST, utilitzant missatges en format JSON tant per a les peticions com per a les respostes.</t>
@@ -4361,7 +4215,6 @@
           <t>CF_M04_AU29</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
         <v>0.7808</v>
       </c>
@@ -4382,7 +4235,6 @@
           <t>Dependency Inversion</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>Inversió de Dependència (DIP): El domini defineix interfícies que són implementades per la infraestructura.</t>
@@ -4474,7 +4326,6 @@
           <t>REST</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Communication between the front-end and the back-end is done through a REST API</t>
@@ -4485,7 +4336,6 @@
           <t>AU_47</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>0.6776</v>
       </c>
@@ -4506,7 +4356,6 @@
           <t>Database</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Data persistence is done using a MySQL relational database, managed through Django's ORM.</t>
@@ -4537,7 +4386,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>application layer, domain layer, infrastructure layer</t>
@@ -4578,7 +4426,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Users: Application customers who use the new features and provide feedback.</t>
@@ -4614,7 +4461,6 @@
           <t>Presentation Layer</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Presentation: manages the application state and communication with the interface user via Bloc/Cubit.</t>
@@ -4650,7 +4496,6 @@
           <t>Google Login</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Authentication services, such as Google login.</t>
@@ -4681,7 +4526,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>data, backend</t>
@@ -4697,7 +4541,6 @@
           <t>AU_43</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>0.7356</v>
       </c>
@@ -4718,7 +4561,6 @@
           <t>Hierarchical model</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>The app's navigation mainly follows a hierarchical model, in which the user accesses the main functionalities from a reduced set of base screens.</t>
@@ -4754,7 +4596,6 @@
           <t>Modular architecture</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Internally, the front-end of the application follows a modular architecture based on features, where code is organized by functionality rather than by type components.</t>
@@ -4790,7 +4631,6 @@
           <t>Bloc/Cubit</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>For state and business logic management, the Bloc pattern is used, specificallythrough its Cubit variant, widely used in Flutter applications modern.</t>
@@ -4826,7 +4666,6 @@
           <t>ORM</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>The database uses MySQL as a relational engine. The tables and relationships are defined using Django's ORM, allowing for easy migration management and ensuring the coherence of the scheme.</t>
@@ -4837,7 +4676,6 @@
           <t>AU_45</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>0.696</v>
       </c>
@@ -4858,7 +4696,6 @@
           <t>Clean Architecture</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>The front-end is implemented with Flutter and follows a structure based on the principles of Clean Architecture, strictly applied.</t>
